--- a/premise/data/additional_inventories/lci-PV-perovskite.xlsx
+++ b/premise/data/additional_inventories/lci-PV-perovskite.xlsx
@@ -1770,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L747"/>
+  <dimension ref="A1:L777"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.83203125" bestFit="1" customWidth="1"/>
@@ -9446,8 +9446,13 @@
       <c r="A437" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B437" s="5" t="s">
-        <v>287</v>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+B10</t>
+        </is>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
@@ -9550,6 +9555,12 @@
         <f>B440</f>
         <v>metallized perovskite cell</v>
       </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
@@ -9762,24 +9773,38 @@
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A456" t="s">
-        <v>306</v>
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+        </is>
       </c>
       <c r="B456">
-        <f>3500/50.7/34916306.0428664</f>
-        <v>1.9771143742193209E-6</v>
-      </c>
-      <c r="C456" t="s">
-        <v>47</v>
-      </c>
-      <c r="E456" t="s">
-        <v>53</v>
+        <f>7.849144065650704e-05</f>
+        <v>7.849144065650704e-05</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="F456" t="s">
         <v>77</v>
       </c>
-      <c r="G456" t="s">
-        <v>305</v>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
@@ -10466,8 +10491,13 @@
       <c r="A503" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B503" s="5" t="s">
-        <v>313</v>
+      <c r="B503" s="5" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+C01. Module capacity: 500 Wp</t>
+        </is>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.2">
@@ -10569,6 +10599,12 @@
       <c r="G511" t="s">
         <v>457</v>
       </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
@@ -10591,26 +10627,37 @@
       </c>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A513" t="s">
-        <v>306</v>
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+        </is>
       </c>
       <c r="B513">
-        <v>3.3530571992109896E-2</v>
-      </c>
-      <c r="C513" t="s">
-        <v>47</v>
-      </c>
-      <c r="E513" t="s">
-        <v>53</v>
+        <v>1.274161735700176</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="F513" t="s">
         <v>77</v>
       </c>
-      <c r="G513" t="s">
-        <v>305</v>
-      </c>
-      <c r="H513" t="s">
-        <v>311</v>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.2">
@@ -14080,6 +14127,560 @@
       </c>
       <c r="G747" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B752">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+        </is>
+      </c>
+      <c r="B759">
+        <v>1</v>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B760">
+        <v>1.0447368421052632</v>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>section bar extrusion, aluminium</t>
+        </is>
+      </c>
+      <c r="B761">
+        <v>1</v>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>section bar extrusion, aluminium</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>section bar extrusion, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>powder coating, aluminium sheet</t>
+        </is>
+      </c>
+      <c r="B762">
+        <v>0.2578947368421053</v>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>powder coat, aluminium sheet</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>powder coat, aluminium sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>market for waste aluminium</t>
+        </is>
+      </c>
+      <c r="B763">
+        <v>-0.044736842105263186</v>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>waste aluminium</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>waste aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B768">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+ Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+        </is>
+      </c>
+      <c r="B775">
+        <v>1</v>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B776">
+        <v>1</v>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B777">
+        <v>1</v>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/premise/data/additional_inventories/lci-PV-perovskite.xlsx
+++ b/premise/data/additional_inventories/lci-PV-perovskite.xlsx
@@ -1770,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L777"/>
+  <dimension ref="A1:L792"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.83203125" bestFit="1" customWidth="1"/>
@@ -11237,8 +11237,15 @@
       <c r="A543" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B543" s="5" t="s">
-        <v>343</v>
+      <c r="B543" s="5" t="inlineStr">
+        <is>
+          <t>APPROVED PEROVSKITE PV BALANCE-OF-SYSTEM COVERAGE, issue 117, 2026-10-19. Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.
+The active electricity chain previously purchased only the module and packaging. Add necessary external mounting, electrical installation and inverter equipment without purchasing a second module or its existing aluminium frame. Adopt an explicit shared slanted-roof installation reference: five 0.5kWp modules share one 2.5kW inverter and building electrical installation. Per module, 2m2 external mounting, 0.5/3 of the electrical installation for 3kWp, and 0.5/2.5 of one inverter at installation.
+Include two inverter purchases over the existing module service horizon (one initial, one replacement). Expected manufactured inverter dose is 0.4 unit per module. At an illustrative 1000kWh/kWp/year, retained 11500kWh/module corresponds to 23 years and a 15-year inverter life would require two discrete purchases; this does not establish an independently measured module calendar life. Sensitivity 1-3 inverter purchases and roof versus ground mounting is required. No second electricity-loss factor: existing 11500kWh is retained as delivered output. Supplier inverter manufacture already includes its packaging and disposal; do not add whole-inverter disposal again.
+Native 2.5kW inverter and mounting/electrical inventories are background material/architecture proxies, not perovskite manufacturer hardware. External mounting is distinct from the existing module frame. Building roof/chassis production is outside this added equipment kit. Electrical installation and support manufacture use existing supplier EOL boundaries; missing collection details are not invented. This closes the previously absent installation boundary, not every semiconductor/installation specification or lifetime uncertainty. Existing module cells, frame, packaging and yield unchanged; no runtime/native/share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+C02</t>
+        </is>
       </c>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.2">
@@ -11341,6 +11348,14 @@
         <f>B546</f>
         <v>photovoltaic panel, perovskite</v>
       </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>APPROVED PEROVSKITE PV BALANCE-OF-SYSTEM COVERAGE, issue 117, 2026-10-19. Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.
+The active electricity chain previously purchased only the module and packaging. Add necessary external mounting, electrical installation and inverter equipment without purchasing a second module or its existing aluminium frame. Adopt an explicit shared slanted-roof installation reference: five 0.5kWp modules share one 2.5kW inverter and building electrical installation. Per module, 2m2 external mounting, 0.5/3 of the electrical installation for 3kWp, and 0.5/2.5 of one inverter at installation.
+Include two inverter purchases over the existing module service horizon (one initial, one replacement). Expected manufactured inverter dose is 0.4 unit per module. At an illustrative 1000kWh/kWp/year, retained 11500kWh/module corresponds to 23 years and a 15-year inverter life would require two discrete purchases; this does not establish an independently measured module calendar life. Sensitivity 1-3 inverter purchases and roof versus ground mounting is required. No second electricity-loss factor: existing 11500kWh is retained as delivered output. Supplier inverter manufacture already includes its packaging and disposal; do not add whole-inverter disposal again.
+Native 2.5kW inverter and mounting/electrical inventories are background material/architecture proxies, not perovskite manufacturer hardware. External mounting is distinct from the existing module frame. Building roof/chassis production is outside this added equipment kit. Electrical installation and support manufacture use existing supplier EOL boundaries; missing collection details are not invented. This closes the previously absent installation boundary, not every semiconductor/installation specification or lifetime uncertainty. Existing module cells, frame, packaging and yield unchanged; no runtime/native/share edits.</t>
+        </is>
+      </c>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
@@ -11405,6 +11420,44 @@
       </c>
       <c r="G554" t="s">
         <v>350</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+        </is>
+      </c>
+      <c r="B555">
+        <v>1</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>APPROVED PEROVSKITE PV BALANCE-OF-SYSTEM COVERAGE, issue 117, 2026-10-19. Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.
+The active electricity chain previously purchased only the module and packaging. Add necessary external mounting, electrical installation and inverter equipment without purchasing a second module or its existing aluminium frame. Adopt an explicit shared slanted-roof installation reference: five 0.5kWp modules share one 2.5kW inverter and building electrical installation. Per module, 2m2 external mounting, 0.5/3 of the electrical installation for 3kWp, and 0.5/2.5 of one inverter at installation.
+Include two inverter purchases over the existing module service horizon (one initial, one replacement). Expected manufactured inverter dose is 0.4 unit per module. At an illustrative 1000kWh/kWp/year, retained 11500kWh/module corresponds to 23 years and a 15-year inverter life would require two discrete purchases; this does not establish an independently measured module calendar life. Sensitivity 1-3 inverter purchases and roof versus ground mounting is required. No second electricity-loss factor: existing 11500kWh is retained as delivered output. Supplier inverter manufacture already includes its packaging and disposal; do not add whole-inverter disposal again.
+Native 2.5kW inverter and mounting/electrical inventories are background material/architecture proxies, not perovskite manufacturer hardware. External mounting is distinct from the existing module frame. Building roof/chassis production is outside this added equipment kit. Electrical installation and support manufacture use existing supplier EOL boundaries; missing collection details are not invented. This closes the previously absent installation boundary, not every semiconductor/installation specification or lifetime uncertainty. Existing module cells, frame, packaging and yield unchanged; no runtime/native/share edits.</t>
+        </is>
       </c>
     </row>
     <row r="556" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -14680,6 +14733,285 @@
       <c r="I777" t="inlineStr">
         <is>
           <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B782">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>APPROVED PEROVSKITE PV BALANCE-OF-SYSTEM COVERAGE, issue 117, 2026-10-19. Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.
+The active electricity chain previously purchased only the module and packaging. Add necessary external mounting, electrical installation and inverter equipment without purchasing a second module or its existing aluminium frame. Adopt an explicit shared slanted-roof installation reference: five 0.5kWp modules share one 2.5kW inverter and building electrical installation. Per module, 2m2 external mounting, 0.5/3 of the electrical installation for 3kWp, and 0.5/2.5 of one inverter at installation.
+Include two inverter purchases over the existing module service horizon (one initial, one replacement). Expected manufactured inverter dose is 0.4 unit per module. At an illustrative 1000kWh/kWp/year, retained 11500kWh/module corresponds to 23 years and a 15-year inverter life would require two discrete purchases; this does not establish an independently measured module calendar life. Sensitivity 1-3 inverter purchases and roof versus ground mounting is required. No second electricity-loss factor: existing 11500kWh is retained as delivered output. Supplier inverter manufacture already includes its packaging and disposal; do not add whole-inverter disposal again.
+Native 2.5kW inverter and mounting/electrical inventories are background material/architecture proxies, not perovskite manufacturer hardware. External mounting is distinct from the existing module frame. Building roof/chassis production is outside this added equipment kit. Electrical installation and support manufacture use existing supplier EOL boundaries; missing collection details are not invented. This closes the previously absent installation boundary, not every semiconductor/installation specification or lifetime uncertainty. Existing module cells, frame, packaging and yield unchanged; no runtime/native/share edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+        </is>
+      </c>
+      <c r="B789">
+        <v>1</v>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>market for inverter, 2.5kW</t>
+        </is>
+      </c>
+      <c r="B790">
+        <v>0.4</v>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>inverter, 2.5kW</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>inverter, 2.5kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>market for photovoltaic mounting system, for slanted-roof installation</t>
+        </is>
+      </c>
+      <c r="B791">
+        <v>2</v>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>photovoltaic mounting system, for slanted-roof installation</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>photovoltaic mounting system, for slanted-roof installation</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>market for photovoltaics, electric installation for 3kWp module, at building</t>
+        </is>
+      </c>
+      <c r="B792">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>photovoltaics, electric installation for 3kWp module, at building</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>photovoltaics, electric installation for 3kWp module, at building</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-PV-perovskite.xlsx
+++ b/premise/data/additional_inventories/lci-PV-perovskite.xlsx
@@ -9775,7 +9775,7 @@
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" t="inlineStr">
         <is>
-          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+          <t xml:space="preserve">aluminium production, for photovoltaic cell metallization</t>
         </is>
       </c>
       <c r="B456">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -10629,7 +10629,7 @@
     <row r="513" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A513" t="inlineStr">
         <is>
-          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+          <t xml:space="preserve">aluminium profile production, photovoltaic frame</t>
         </is>
       </c>
       <c r="B513">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -11425,7 +11425,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kWp</t>
         </is>
       </c>
       <c r="B555">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+          <t xml:space="preserve">aluminium profile production, photovoltaic frame</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
         </is>
       </c>
     </row>
@@ -14260,7 +14260,8 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: aluminium PV frame profile, retained metal-budget engineering reference. Former reference product: aluminium PV frame profile, retained metal-budget engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
  Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
         </is>
       </c>
@@ -14322,7 +14323,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+          <t xml:space="preserve">aluminium profile production, photovoltaic frame</t>
         </is>
       </c>
       <c r="B759">
@@ -14345,12 +14346,12 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>aluminium PV frame profile, retained metal-budget engineering reference</t>
+          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14503,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+          <t xml:space="preserve">aluminium production, for photovoltaic cell metallization</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14537,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14573,8 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: aluminium material for PV cell-contact manufacture, engineering reference. Former reference product: aluminium material for PV cell-contact manufacture, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
  Cellcontactstagehasnoprovenframefunction. PreserveitscurrentgrossAlbudget7.849144065650704e-05kg/cell equivalent andsupplyordinaryAlmaterialwithsheetrollingasexplicitforminganalogue,instead ofapplyingthermallybrokenwindowconstructiontoamicrogrammetalinput. ThisdoesNOTassertsourcefilmthickness,contactmetallurgyororiginalpartidentity;actualfunctionstillunresolved. Its existing3.9857213559708595e-05kgAlstagewaste isretainedEXACTLY,soimpliedAlremaining=3.863422709679845e-05kg/cell;doNOTaddasecondmanufacturinglossorwholeframeEOLthere. Moduleprofilemanufacturingoffcutsareaddedonceinsideprofilehelper;sourcewholemoduleEOLboundaryisretained,withoutinventinganadditionalfinishedframecollection/recyclingroute. GenericwasteAlmarket istheretainedmanufacturingfateproxy,noextraavoidedmetalcreditorprimary/secondaryshare. Powdercoatingcurrentnativeprocessburdenalreadyincludespaintmanufacture;donotaddpaintagain. Wroughtalloymixandrollingservicesarematerial/shapeproxies,notcertifiedPValloyorhighpuritycontactgrade. Retaincellcount,moduleefficiency,installedarea,lifetimeyieldandallpurchasedenergy. Explicitlycarryoriginalsource/grade/geometry/EOLgapsforward;thiscorrectscomponentboundaryonly,notcompletePValuminiumvalidation. Existingworkbookonly,no runtime/native edits.</t>
         </is>
       </c>
@@ -14634,7 +14636,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+          <t xml:space="preserve">aluminium production, for photovoltaic cell metallization</t>
         </is>
       </c>
       <c r="B775">
@@ -14657,12 +14659,12 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>aluminium material for PV cell-contact manufacture, engineering reference</t>
+          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14746,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kWp</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14780,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
         </is>
       </c>
     </row>
@@ -14814,7 +14816,8 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>APPROVED PEROVSKITE PV BALANCE-OF-SYSTEM COVERAGE, issue 117, 2026-10-19. Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: perovskite PV balance of system, shared 0.5kWp module reference. Former reference product: perovskite PV balance of system, shared 0.5kWp module reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PEROVSKITE PV BALANCE-OF-SYSTEM COVERAGE, issue 117, 2026-10-19. Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.
 The active electricity chain previously purchased only the module and packaging. Add necessary external mounting, electrical installation and inverter equipment without purchasing a second module or its existing aluminium frame. Adopt an explicit shared slanted-roof installation reference: five 0.5kWp modules share one 2.5kW inverter and building electrical installation. Per module, 2m2 external mounting, 0.5/3 of the electrical installation for 3kWp, and 0.5/2.5 of one inverter at installation.
 Include two inverter purchases over the existing module service horizon (one initial, one replacement). Expected manufactured inverter dose is 0.4 unit per module. At an illustrative 1000kWh/kWp/year, retained 11500kWh/module corresponds to 23 years and a 15-year inverter life would require two discrete purchases; this does not establish an independently measured module calendar life. Sensitivity 1-3 inverter purchases and roof versus ground mounting is required. No second electricity-loss factor: existing 11500kWh is retained as delivered output. Supplier inverter manufacture already includes its packaging and disposal; do not add whole-inverter disposal again.
 Native 2.5kW inverter and mounting/electrical inventories are background material/architecture proxies, not perovskite manufacturer hardware. External mounting is distinct from the existing module frame. Building roof/chassis production is outside this added equipment kit. Electrical installation and support manufacture use existing supplier EOL boundaries; missing collection details are not invented. This closes the previously absent installation boundary, not every semiconductor/installation specification or lifetime uncertainty. Existing module cells, frame, packaging and yield unchanged; no runtime/native/share edits.</t>
@@ -14878,7 +14881,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kWp</t>
         </is>
       </c>
       <c r="B789">
@@ -14901,12 +14904,12 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>perovskite PV balance of system, shared 0.5kWp module reference</t>
+          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-PV-perovskite.xlsx
+++ b/premise/data/additional_inventories/lci-PV-perovskite.xlsx
@@ -1770,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L792"/>
+  <dimension ref="A1:L795"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.83203125" bestFit="1" customWidth="1"/>
@@ -11425,7 +11425,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kWp</t>
+          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kwp</t>
         </is>
       </c>
       <c r="B555">
@@ -14269,100 +14269,77 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B758" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C758" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D758" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E758" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F758" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G758" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H758" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I758" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t xml:space="preserve">aluminium profile production, photovoltaic frame</t>
-        </is>
-      </c>
-      <c r="B759">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
+          <t xml:space="preserve">aluminium profile production, photovoltaic frame</t>
         </is>
       </c>
       <c r="B760">
-        <v>1.0447368421052632</v>
+        <v>1</v>
       </c>
       <c r="C760" t="inlineStr">
         <is>
@@ -14376,32 +14353,32 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t xml:space="preserve">aluminium profile, photovoltaic frame</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>section bar extrusion, aluminium</t>
+          <t>market for aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="B761">
-        <v>1</v>
+        <v>1.0447368421052632</v>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -14416,23 +14393,23 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>section bar extrusion, aluminium</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>section bar extrusion, aluminium</t>
+          <t>aluminium, wrought alloy</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>powder coating, aluminium sheet</t>
+          <t>section bar extrusion, aluminium</t>
         </is>
       </c>
       <c r="B762">
-        <v>0.2578947368421053</v>
+        <v>1</v>
       </c>
       <c r="C762" t="inlineStr">
         <is>
@@ -14441,7 +14418,7 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>square meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
@@ -14451,127 +14428,162 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>powder coat, aluminium sheet</t>
+          <t>section bar extrusion, aluminium</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>powder coat, aluminium sheet</t>
+          <t>section bar extrusion, aluminium</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
+          <t>powder coating, aluminium sheet</t>
+        </is>
+      </c>
+      <c r="B763">
+        <v>0.2578947368421053</v>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>powder coat, aluminium sheet</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>powder coat, aluminium sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
           <t>market for waste aluminium</t>
         </is>
       </c>
-      <c r="B763">
+      <c r="B764">
         <v>-0.044736842105263186</v>
       </c>
-      <c r="C763" t="inlineStr">
+      <c r="C764" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr">
+      <c r="D764" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F763" t="inlineStr">
+      <c r="F764" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G763" t="inlineStr">
+      <c r="G764" t="inlineStr">
         <is>
           <t>waste aluminium</t>
         </is>
       </c>
-      <c r="I763" t="inlineStr">
+      <c r="I764" t="inlineStr">
         <is>
           <t>waste aluminium</t>
-        </is>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B766" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium production, for photovoltaic cell metallization</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">aluminium production, for photovoltaic cell metallization</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B768">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B769" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B769">
+        <v>1</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel.</t>
+          <t>kilogram</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
+      <c r="B773" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: aluminium material for PV cell-contact manufacture, engineering reference. Former reference product: aluminium material for PV cell-contact manufacture, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED PV PROFILE / THERMAL-WINDOW BOUNDARY, issue113,2026-10-18. Roffeis et al.2022 DOI10.1039/D2SE00096B; workbookmoduleexchange comment explicitly originalGaBipowdercoatedAlprofile. OriginalRSCsupplementsretrieval2026-10-18 returned404/403;originalprofilekgandcellcontactAlfunctionnotrecovered. Native3.12RERthermalwindowframe read-onlymaterialscreen39.7kgwroughtAl,38kgextrusion,9.8m2powdercoat perm2window reference,plusrubber,thermalbreakpolymers,reinforcingandstainlesssteel. Explicitengineeringfallbackwhileoriginalmassbasisremainsgap:preserveCURRENTGROSSAlpurchaseatbothstages,doNOTclaimrecoveredsourceprofilemass. Moduletakes1.3311637080867629kgwroughtalloy pernominalm2module;adoptfinishedprofile1.274161735700176kg fromtheexisting38/39.7extrusion-to-feedratio. Thisratioisanengineeringyieldinterpretationoftheoldproxy,notmeasuredPV extrusionyield. New1kgfinishedprofileuses1.0447368421052632kgwroughtAl,1kgextrusion,0.2578947368421053m2powdercoating and0.044736842105263186kgmanufacturingAlwaste. Keepmodulepowdercoatingarea=0.32859960552267703m2 andgrossAlpurchaseexactly;removeunsupportedthermalwindowrubber,glassfibre/polyamidethermalbreaks,ABS,reinforcing/stainlesssteelandwindowfactoryextras. RetainallseparatelylistedPVglass,adhesive,junction-boxpolymers,Cuwires,soldersandothernecessaryseals/fasteners;no secondmodulemanufacture. At2m2nominal500Wpinstallationthismeans2.548323471400352kgfinishedprofile,notvalidatedactualframegeometry. GrossAlbudgetandgradeareunresolvedsourceassumptions;sensitivity.5-2xretainedframeAl and90-100%manufacturingyield,holdinggross/net/scrapcoherent.
@@ -14579,134 +14591,76 @@
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C774" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D774" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E774" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F774" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G774" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H774" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I774" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t xml:space="preserve">aluminium production, for photovoltaic cell metallization</t>
-        </is>
-      </c>
-      <c r="B775">
-        <v>1</v>
-      </c>
-      <c r="C775" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D775" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F775" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G775" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
-        </is>
-      </c>
-      <c r="I775" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>market for aluminium, wrought alloy</t>
-        </is>
-      </c>
-      <c r="B776">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>aluminium, wrought alloy</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>market for sheet rolling, aluminium</t>
+          <t xml:space="preserve">aluminium production, for photovoltaic cell metallization</t>
         </is>
       </c>
       <c r="B777">
@@ -14724,97 +14678,167 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aluminium, for photovoltaic cell metallization</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B778">
+        <v>1</v>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G777" t="inlineStr">
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B779">
+        <v>1</v>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
         <is>
           <t>sheet rolling, aluminium</t>
         </is>
       </c>
-      <c r="I777" t="inlineStr">
+      <c r="I779" t="inlineStr">
         <is>
           <t>sheet rolling, aluminium</t>
-        </is>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B780" t="inlineStr">
-        <is>
-          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kWp</t>
-        </is>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B781" t="inlineStr">
-        <is>
-          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B782">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kwp</t>
+        </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B784" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B784">
+        <v>1</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.</t>
+          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
+      <c r="B788" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: perovskite PV balance of system, shared 0.5kWp module reference. Former reference product: perovskite PV balance of system, shared 0.5kWp module reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED PEROVSKITE PV BALANCE-OF-SYSTEM COVERAGE, issue 117, 2026-10-19. Roffeis et al.2022, DOI10.1039/D2SE00096B; existing workbook 0.5kWp, 2m2 module, 11500kWh lifetime output. Balance-of-system supplier conventions aligned with the existing GaAs installation in lci-PV-GaAs.xlsx; original Roffeis supplementary installation specification not recovered.
@@ -14824,195 +14848,207 @@
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B788" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C788" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D788" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E788" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F788" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G788" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H788" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I788" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kWp</t>
-        </is>
-      </c>
-      <c r="B789">
-        <v>1</v>
-      </c>
-      <c r="C789" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D789" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F789" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G789" t="inlineStr">
-        <is>
-          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
-        </is>
-      </c>
-      <c r="I789" t="inlineStr">
-        <is>
-          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>market for inverter, 2.5kW</t>
-        </is>
-      </c>
-      <c r="B790">
-        <v>0.4</v>
-      </c>
-      <c r="C790" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D790" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="F790" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G790" t="inlineStr">
-        <is>
-          <t>inverter, 2.5kW</t>
-        </is>
-      </c>
-      <c r="I790" t="inlineStr">
-        <is>
-          <t>inverter, 2.5kW</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>market for photovoltaic mounting system, for slanted-roof installation</t>
-        </is>
-      </c>
-      <c r="B791">
-        <v>2</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>square meter</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>photovoltaic mounting system, for slanted-roof installation</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>photovoltaic mounting system, for slanted-roof installation</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
+          <t xml:space="preserve">photovoltaic balance of system production, perovskite, 0.5 kwp</t>
+        </is>
+      </c>
+      <c r="B792">
+        <v>1</v>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t xml:space="preserve">photovoltaic balance of system, perovskite, 0.5 kWp</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>market for inverter, 2.5kW</t>
+        </is>
+      </c>
+      <c r="B793">
+        <v>0.4</v>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>inverter, 2.5kW</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>inverter, 2.5kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>market for photovoltaic mounting system, for slanted-roof installation</t>
+        </is>
+      </c>
+      <c r="B794">
+        <v>2</v>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>photovoltaic mounting system, for slanted-roof installation</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>photovoltaic mounting system, for slanted-roof installation</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
           <t>market for photovoltaics, electric installation for 3kWp module, at building</t>
         </is>
       </c>
-      <c r="B792">
+      <c r="B795">
         <v>0.16666666666666666</v>
       </c>
-      <c r="C792" t="inlineStr">
+      <c r="C795" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D792" t="inlineStr">
+      <c r="D795" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="F792" t="inlineStr">
+      <c r="F795" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G792" t="inlineStr">
+      <c r="G795" t="inlineStr">
         <is>
           <t>photovoltaics, electric installation for 3kWp module, at building</t>
         </is>
       </c>
-      <c r="I792" t="inlineStr">
+      <c r="I795" t="inlineStr">
         <is>
           <t>photovoltaics, electric installation for 3kWp module, at building</t>
         </is>
